--- a/test prices.xlsx
+++ b/test prices.xlsx
@@ -1,90 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\PycharmProjects\PandasConsolidate\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C384DDBD-40C9-4AC8-881F-347BF5DE3806}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4875" yWindow="3435" windowWidth="21600" windowHeight="12735" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="4875" yWindow="3435" windowWidth="21600" windowHeight="12735" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Table" sheetId="1" r:id="rId1"/>
-    <sheet name="Charts" sheetId="2" r:id="rId2"/>
+    <sheet name="Table" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Charts" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="15">
-  <si>
-    <t>xxx</t>
-  </si>
-  <si>
-    <t>Pricing Category</t>
-  </si>
-  <si>
-    <t>Percentage</t>
-  </si>
-  <si>
-    <t>A</t>
-  </si>
-  <si>
-    <t>B</t>
-  </si>
-  <si>
-    <t>C</t>
-  </si>
-  <si>
-    <t>D</t>
-  </si>
-  <si>
-    <t>E</t>
-  </si>
-  <si>
-    <t>F</t>
-  </si>
-  <si>
-    <t>G</t>
-  </si>
-  <si>
-    <t>H</t>
-  </si>
-  <si>
-    <t>I</t>
-  </si>
-  <si>
-    <t>K</t>
-  </si>
-  <si>
-    <t>yyy</t>
-  </si>
-  <si>
-    <t>zzz</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
+      <name val="Aptos Narrow"/>
+      <charset val="204"/>
+      <family val="2"/>
+      <color theme="1"/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <charset val="204"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -103,22 +48,419 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Percentage for xxx</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <varyColors val="0"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Charts'!$A$3:$A$12</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Charts'!$B$3:$B$12</f>
+            </numRef>
+          </val>
+        </ser>
+        <dLbls>
+          <showLegendKey val="0"/>
+          <showVal val="1"/>
+          <showCatName val="0"/>
+          <showSerName val="0"/>
+        </dLbls>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+          <max val="100"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Percentage for yyy</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <varyColors val="0"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Charts'!$A$16:$A$25</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Charts'!$B$16:$B$25</f>
+            </numRef>
+          </val>
+        </ser>
+        <dLbls>
+          <showLegendKey val="0"/>
+          <showVal val="1"/>
+          <showCatName val="0"/>
+          <showSerName val="0"/>
+        </dLbls>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+          <max val="100"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Percentage for zzz</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <varyColors val="0"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Charts'!$A$29:$A$38</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Charts'!$B$29:$B$38</f>
+            </numRef>
+          </val>
+        </ser>
+        <dLbls>
+          <showLegendKey val="0"/>
+          <showVal val="1"/>
+          <showCatName val="0"/>
+          <showSerName val="0"/>
+        </dLbls>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+          <max val="100"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <twoCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>2</row>
+      <rowOff>0</rowOff>
+    </from>
+    <to>
+      <col>10</col>
+      <colOff>0</colOff>
+      <row>12</row>
+      <rowOff>0</rowOff>
+    </to>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>15</row>
+      <rowOff>0</rowOff>
+    </from>
+    <to>
+      <col>10</col>
+      <colOff>0</colOff>
+      <row>25</row>
+      <rowOff>0</rowOff>
+    </to>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="2" name="Chart 2"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>28</row>
+      <rowOff>0</rowOff>
+    </from>
+    <to>
+      <col>10</col>
+      <colOff>0</colOff>
+      <row>38</row>
+      <rowOff>0</rowOff>
+    </to>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="3" name="Chart 3"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </twoCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -437,303 +779,390 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:B38"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col width="15.28515625" bestFit="1" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>xxx</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Pricing Category</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Percentage</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>7</v>
-      </c>
-      <c r="B7">
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
         <v>25</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8">
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
         <v>50</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>yyy</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Pricing Category</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Percentage</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
         <v>10</v>
       </c>
-      <c r="B10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>11</v>
-      </c>
-      <c r="B11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>12</v>
-      </c>
-      <c r="B12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>1</v>
-      </c>
-      <c r="B15" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>3</v>
-      </c>
-      <c r="B16">
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
         <v>10</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>4</v>
-      </c>
-      <c r="B17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>5</v>
-      </c>
-      <c r="B18">
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
         <v>10</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>6</v>
-      </c>
-      <c r="B19">
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
         <v>10</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>7</v>
-      </c>
-      <c r="B20">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>8</v>
-      </c>
-      <c r="B21">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>9</v>
-      </c>
-      <c r="B22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
         <v>10</v>
       </c>
-      <c r="B23">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>11</v>
-      </c>
-      <c r="B24">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>12</v>
-      </c>
-      <c r="B25">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>1</v>
-      </c>
-      <c r="B28" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>3</v>
-      </c>
-      <c r="B29">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>4</v>
-      </c>
-      <c r="B30">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>5</v>
-      </c>
-      <c r="B31">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>6</v>
-      </c>
-      <c r="B32">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>7</v>
-      </c>
-      <c r="B33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>8</v>
-      </c>
-      <c r="B34">
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>zzz</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Pricing Category</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Percentage</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
         <v>100</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>9</v>
-      </c>
-      <c r="B35">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>10</v>
-      </c>
-      <c r="B36">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>11</v>
-      </c>
-      <c r="B37">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>12</v>
-      </c>
-      <c r="B38">
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>